--- a/corpus/evenki/meta.xlsx
+++ b/corpus/evenki/meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompLing\CorpusUtils\tsakorpus\corpus\evenki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31178DA6-9EF7-471A-9E55-C2A13C5DC338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A2A6EB-E494-4061-BFD0-64F4D3C38B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="13329" xr2:uid="{771BC294-5EBD-4042-B8CE-35ED2E940EB8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="549">
   <si>
     <t>filename</t>
   </si>
@@ -1678,6 +1678,12 @@
   </si>
   <si>
     <t>Путугир Петр Николаевич</t>
+  </si>
+  <si>
+    <t>Соболь</t>
+  </si>
+  <si>
+    <t>https://siberian-lang.iling-ran.ru/ru/node/4889421</t>
   </si>
 </sst>
 </file>
@@ -2043,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B59A00EB-A29E-4129-86BE-B163293E25C7}">
-  <dimension ref="A1:L150"/>
+  <dimension ref="A1:L151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="78.09765625" bestFit="1" customWidth="1"/>
@@ -7692,6 +7698,44 @@
         <v>338</v>
       </c>
       <c r="L150" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>279</v>
+      </c>
+      <c r="B151" t="s">
+        <v>280</v>
+      </c>
+      <c r="C151">
+        <v>1952</v>
+      </c>
+      <c r="D151" t="s">
+        <v>281</v>
+      </c>
+      <c r="E151" t="s">
+        <v>547</v>
+      </c>
+      <c r="F151" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151">
+        <v>1952</v>
+      </c>
+      <c r="H151">
+        <v>1952</v>
+      </c>
+      <c r="I151" t="s">
+        <v>548</v>
+      </c>
+      <c r="J151" t="s">
+        <v>26</v>
+      </c>
+      <c r="K151" t="s">
+        <v>336</v>
+      </c>
+      <c r="L151" t="s">
         <v>451</v>
       </c>
     </row>

--- a/corpus/evenki/meta.xlsx
+++ b/corpus/evenki/meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompLing\CorpusUtils\tsakorpus\corpus\evenki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A2A6EB-E494-4061-BFD0-64F4D3C38B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DF672F-CA34-4894-A6F4-831FB9463014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="13329" xr2:uid="{771BC294-5EBD-4042-B8CE-35ED2E940EB8}"/>
   </bookViews>
